--- a/thanks/freelance-pricing-kit/files/freelance-pricing-kit.xlsx
+++ b/thanks/freelance-pricing-kit/files/freelance-pricing-kit.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="181">
   <si>
     <t>Freelance Pricing &amp; Quote Kit: start here</t>
   </si>
   <si>
-    <t>Works in Excel and Google Sheets. Currency-neutral: amounts have no currency sign, use your own. Planning tool, not tax, legal or financial advice.</t>
+    <t>Works in Excel and Google Sheets. Currency-neutral: amounts have no currency sign, so use your own. Planning tool, not tax, legal or financial advice.</t>
   </si>
   <si>
     <t>Step</t>
@@ -33,31 +33,31 @@
     <t>1. Floor Rate</t>
   </si>
   <si>
-    <t>Replace Maya's example values in the yellow YOUR INPUT column with your own numbers.</t>
+    <t>Replace Maya's example values in the yellow cells with your own numbers (income goal, costs, tax, working weeks, billable share).</t>
   </si>
   <si>
     <t>2. Read your floor</t>
   </si>
   <si>
-    <t>The RESULT column shows your floor hourly rate (rounded up to nearest 5) and day rate. Never quote below it.</t>
+    <t>The blue cells show your floor hourly rate (rounded up to the nearest 5) and day rate. Never quote below the floor.</t>
   </si>
   <si>
     <t>3. Market Check</t>
   </si>
   <si>
-    <t>Enter up to 5 rates you have seen for similar work (with a source note) and the rate you plan to quote. BELOW FLOOR = too low.</t>
+    <t>Enter up to 5 rates you have seen for similar work, with a note on the source. Enter the rate you plan to quote. The tab shows BELOW FLOOR if it is too low.</t>
   </si>
   <si>
     <t>4. 3-Tier Quote</t>
   </si>
   <si>
-    <t>List a real project's tasks (up to 15 rows) with hours and tier: 1 = all packages, 2 = Standard + Premium, 3 = Premium only.</t>
+    <t>List the tasks of a real project (up to 15 rows) with hours and a tier (dropdown): 1 = in all packages, 2 = Standard and Premium, 3 = Premium only.</t>
   </si>
   <si>
     <t>5. Quote settings</t>
   </si>
   <si>
-    <t>Below the task list: contingency %, deposit %, rounding step. Leave 'Quote rate override' empty to quote at your floor.</t>
+    <t>Set contingency %, deposit % and rounding step. Leave "Quote rate override" empty to quote at your floor rate, or type a higher rate.</t>
   </si>
   <si>
     <t>6. Send the quote</t>
@@ -69,49 +69,49 @@
     <t>7. Change Order</t>
   </si>
   <si>
-    <t>When the client asks for something extra, enter hours and rush multiplier (1, 1.25 or 1.5) to price it before you start.</t>
+    <t>When the client asks for something extra, enter the hours and pick the rush multiplier from the dropdown in cell B8 (1 / 1.25 / 1.5) to get the price before you start the work.</t>
   </si>
   <si>
     <t>8. Rate Increase</t>
   </si>
   <si>
-    <t>Test a new rate: monthly revenue before/after and the break-even client loss %.</t>
+    <t>Test a new rate: see your monthly revenue before and after, and how much client work you could lose and still earn the same.</t>
   </si>
   <si>
     <t>9. Check the example</t>
   </si>
   <si>
-    <t>Maya's example values give: floor rate 90, day rate 720, packages 1,900 / 2,700 / 3,250, deposits 950 / 1,350 / 1,625.</t>
-  </si>
-  <si>
-    <t>COLOR LEGEND</t>
-  </si>
-  <si>
-    <t>YELLOW cells</t>
-  </si>
-  <si>
-    <t>YOUR INPUT: type your numbers or text here. They start with Maya's values (Maya Ortiz is a fictional example).</t>
-  </si>
-  <si>
-    <t>RESULT / FORMULA columns</t>
-  </si>
-  <si>
-    <t>FORMULA, DON'T TYPE: calculated for you. Typing over one deletes its formula (Ctrl+Z / Cmd+Z undoes it).</t>
-  </si>
-  <si>
-    <t>Protect your formulas</t>
-  </si>
-  <si>
-    <t>Optional: Excel: Review &gt; Protect Sheet (no password). Google Sheets: Data &gt; Protect sheets and ranges.</t>
-  </si>
-  <si>
-    <t>Add the rush dropdown</t>
-  </si>
-  <si>
-    <t>Optional: Change Order, cell B7. Excel: Data &gt; Data Validation &gt; List, source 1,1.25,1.5. Sheets: Data &gt; Data validation &gt; Dropdown.</t>
-  </si>
-  <si>
-    <t>TABS (click to open)</t>
+    <t>With Maya's example values: floor rate 90, day rate 720, packages 1,900 / 2,700 / 3,250. The PDF guide walks through the same numbers.</t>
+  </si>
+  <si>
+    <t>10. Protection</t>
+  </si>
+  <si>
+    <t>Sheets are protected WITHOUT a password: only the yellow cells can be edited, so formulas are not overwritten by accident. To edit formulas: Excel: Review &gt; Unprotect Sheet. Google Sheets: Data &gt; Protect sheets and ranges.</t>
+  </si>
+  <si>
+    <t>Colour legend</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>YOUR INPUT</t>
+  </si>
+  <si>
+    <t>Yellow cells: type your numbers or text here. They start with Maya's example values.</t>
+  </si>
+  <si>
+    <t>FORMULA, DON'T TYPE</t>
+  </si>
+  <si>
+    <t>Blue cells: calculated for you and locked. They update as soon as you change an input.</t>
+  </si>
+  <si>
+    <t>Tabs (click in Excel)</t>
+  </si>
+  <si>
+    <t>What it does (in Google Sheets, use the tabs at the bottom)</t>
   </si>
   <si>
     <t>The lowest hourly and day rate that still pays your income goal, costs, tax and buffer.</t>
@@ -129,30 +129,30 @@
     <t>Revenue before and after a rate increase, and the break-even client loss %.</t>
   </si>
   <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>Questions or problems: chenphien@gmail.com</t>
+    <t>Questions or problems: use the contact details on the Terms page of the shop where you bought this kit.</t>
+  </si>
+  <si>
+    <t>Maya Ortiz is a fictional example. Replace her numbers with yours.</t>
   </si>
   <si>
     <t>Floor Rate: the lowest hourly rate that still pays you</t>
   </si>
   <si>
-    <t>Type in the yellow YOUR INPUT column (rows 5-12). Rows 13-19 are results in column C: formulas, don't type. Pre-filled with Maya's example.</t>
+    <t>Type in the yellow cells. Blue cells are formulas (locked). Pre-filled with Maya's example. Planning tool, not tax or financial advice.</t>
   </si>
   <si>
     <t>Item</t>
   </si>
   <si>
-    <t>YOUR INPUT</t>
-  </si>
-  <si>
-    <t>RESULT (FORMULA, DON'T TYPE)</t>
+    <t>Value</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>YOUR INPUT (yellow cells: type here)</t>
+  </si>
+  <si>
     <t>Take-home income goal per year (after tax)</t>
   </si>
   <si>
@@ -201,6 +201,9 @@
     <t>Hours you count as one billable day</t>
   </si>
   <si>
+    <t>RESULTS (blue cells: FORMULA, DON'T TYPE)</t>
+  </si>
+  <si>
     <t>Revenue needed per year</t>
   </si>
   <si>
@@ -222,7 +225,7 @@
     <t>FLOOR HOURLY RATE (rounded up to nearest 5)</t>
   </si>
   <si>
-    <t>Never quote below this. The other tabs use it.</t>
+    <t>Never quote below this. Used by the other tabs.</t>
   </si>
   <si>
     <t>FLOOR DAY RATE</t>
@@ -240,49 +243,43 @@
     <t>Billable hours per working week</t>
   </si>
   <si>
-    <t>Reality check: can you sell this many hours every week?</t>
+    <t>A reality check: can you sell this many hours every week?</t>
   </si>
   <si>
     <t>Market Check: is the rate you plan to quote safe?</t>
   </si>
   <si>
-    <t>Rows 5-9: up to 5 hourly rates you have actually seen for similar work, with the source. Row 11: the rate you plan to quote. Results are in column D.</t>
+    <t>Add up to 5 hourly rates you have actually seen for similar work (peer rate pages, community surveys in your niche, agencies you subcontract for). Note the source.</t>
+  </si>
+  <si>
+    <t>Reference (YOUR INPUT)</t>
   </si>
   <si>
     <t>Hourly rate (YOUR INPUT)</t>
   </si>
   <si>
-    <t>Source note (YOUR INPUT)</t>
+    <t>Source note: where, when, what experience level (YOUR INPUT)</t>
   </si>
   <si>
     <t>Reference 1</t>
   </si>
   <si>
-    <t>e.g. a peer's public rate page, with date</t>
-  </si>
-  <si>
     <t>Reference 2</t>
   </si>
   <si>
-    <t>e.g. a community rate survey in your niche</t>
-  </si>
-  <si>
     <t>Reference 3</t>
   </si>
   <si>
-    <t>e.g. what an agency pays you as a subcontractor</t>
-  </si>
-  <si>
     <t>Reference 4</t>
   </si>
   <si>
     <t>Reference 5</t>
   </si>
   <si>
-    <t>RATE I'LL QUOTE (per hour)</t>
-  </si>
-  <si>
-    <t>Maya quotes at her floor (90). Quote higher if your market pays more.</t>
+    <t>Rate I'll quote (per hour)</t>
+  </si>
+  <si>
+    <t>YOUR INPUT. Maya quotes at her floor (90). Quote higher if your market pays more.</t>
   </si>
   <si>
     <t>Your floor rate</t>
@@ -309,7 +306,7 @@
     <t>FLOOR CHECK</t>
   </si>
   <si>
-    <t>BELOW FLOOR: raise the rate or cut scope, never the rate</t>
+    <t>BELOW FLOOR means: raise the rate or cut scope, never the rate</t>
   </si>
   <si>
     <t>MARKET CHECK</t>
@@ -321,25 +318,61 @@
     <t>3-Tier Quote: Essential / Standard / Premium</t>
   </si>
   <si>
-    <t>Rows 5-19: tasks with hours and tier (1 = all packages, 2 = Standard + Premium, 3 = Premium only). Settings in rows 22-25. Package results in columns D-F, rows 29-33.</t>
-  </si>
-  <si>
-    <t>Task / setting</t>
-  </si>
-  <si>
-    <t>Hours or value (YOUR INPUT)</t>
-  </si>
-  <si>
-    <t>Tier 1, 2 or 3 (YOUR INPUT)</t>
-  </si>
-  <si>
-    <t>ESSENTIAL (FORMULA)</t>
-  </si>
-  <si>
-    <t>STANDARD (FORMULA) recommended</t>
-  </si>
-  <si>
-    <t>PREMIUM (FORMULA)</t>
+    <t>Price = hours x quote rate x (1 + contingency), rounded UP to the rounding step. Tier 1 = all packages, tier 2 = Standard + Premium, tier 3 = Premium only.</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Floor rate (from Floor Rate tab)</t>
+  </si>
+  <si>
+    <t>Quote rate override (leave empty to use floor)</t>
+  </si>
+  <si>
+    <t>YOUR INPUT. Type a higher market rate here if you have one</t>
+  </si>
+  <si>
+    <t>QUOTE RATE USED</t>
+  </si>
+  <si>
+    <t>Contingency</t>
+  </si>
+  <si>
+    <t>YOUR INPUT. 10-20% covers email, calls, small surprises</t>
+  </si>
+  <si>
+    <t>Deposit</t>
+  </si>
+  <si>
+    <t>YOUR INPUT. Commonly 30-50%, paid before work starts</t>
+  </si>
+  <si>
+    <t>Rounding step</t>
+  </si>
+  <si>
+    <t>YOUR INPUT. Prices round UP to this step</t>
+  </si>
+  <si>
+    <t>Task (YOUR INPUT)</t>
+  </si>
+  <si>
+    <t>Hours (YOUR INPUT)</t>
+  </si>
+  <si>
+    <t>Tier 1, 2 or 3 (YOUR INPUT, dropdown)</t>
+  </si>
+  <si>
+    <t>Essential h (FORMULA)</t>
+  </si>
+  <si>
+    <t>Standard h (FORMULA)</t>
+  </si>
+  <si>
+    <t>Premium h (FORMULA)</t>
   </si>
   <si>
     <t>Discovery call &amp; brief</t>
@@ -363,46 +396,40 @@
     <t>TOTAL HOURS PER PACKAGE</t>
   </si>
   <si>
-    <t>Quote rate override (leave empty = floor rate)</t>
-  </si>
-  <si>
-    <t>Contingency</t>
-  </si>
-  <si>
-    <t>Deposit</t>
-  </si>
-  <si>
-    <t>Rounding step (prices round UP to this)</t>
-  </si>
-  <si>
-    <t>Floor rate (from Floor Rate tab)</t>
-  </si>
-  <si>
-    <t>QUOTE RATE USED</t>
-  </si>
-  <si>
-    <t>Raw price: hours x rate x (1 + contingency)</t>
-  </si>
-  <si>
-    <t>PRICE (rounded up to rounding step)</t>
-  </si>
-  <si>
-    <t>Deposit (before work starts)</t>
+    <t>Package (FORMULA, DON'T TYPE)</t>
+  </si>
+  <si>
+    <t>Hours</t>
+  </si>
+  <si>
+    <t>Raw price (hours x rate x contingency)</t>
+  </si>
+  <si>
+    <t>PRICE (rounded up)</t>
   </si>
   <si>
     <t>Balance on delivery</t>
   </si>
   <si>
-    <t>Effective hourly (price / hours)</t>
-  </si>
-  <si>
-    <t>Copy row 30 (prices) and row 31 (deposits) into quote-template.html.</t>
+    <t>Effective hourly</t>
+  </si>
+  <si>
+    <t>Essential</t>
+  </si>
+  <si>
+    <t>Standard (recommend this one)</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>Copy these prices and deposits into quote-template.html. Effective hourly = price / hours (it is above your quote rate because of contingency and rounding).</t>
   </si>
   <si>
     <t>Change Order: price a change before you start it</t>
   </si>
   <si>
-    <t>Price impact = hours x (1 + overhead) x rate x rush multiplier, rounded UP. Maya's example: the client asks for a loyalty card design (4 hours).</t>
+    <t>Price impact = estimated hours x (1 + overhead) x rate x rush multiplier, rounded UP. Example: Maya's client asks for a loyalty card design (4 hours).</t>
   </si>
   <si>
     <t>Estimated hours (incl. communication)</t>
@@ -414,19 +441,19 @@
     <t>Overhead</t>
   </si>
   <si>
-    <t>Typically 10-20%: context switching, admin, re-checking</t>
-  </si>
-  <si>
-    <t>Rush multiplier: 1, 1.25 or 1.5</t>
-  </si>
-  <si>
-    <t>1 = normal, 1.25 = rush, 1.5 = urgent (see row 12 check)</t>
-  </si>
-  <si>
-    <t>Rate override (leave empty = quote rate)</t>
-  </si>
-  <si>
-    <t>Empty = QUOTE RATE USED on the 3-Tier Quote tab</t>
+    <t>Typically 10-20%: context switching, admin, re-testing</t>
+  </si>
+  <si>
+    <t>Rush multiplier (choose from dropdown)</t>
+  </si>
+  <si>
+    <t>Dropdown: 1 = normal, 1.25 = rush, 1.5 = urgent</t>
+  </si>
+  <si>
+    <t>Rate override (leave empty to use quote rate)</t>
+  </si>
+  <si>
+    <t>Empty = the quote rate from the 3-Tier Quote tab</t>
   </si>
   <si>
     <t>Round up to nearest</t>
@@ -441,12 +468,6 @@
     <t>The package the client accepted (Maya: Standard, 2,700)</t>
   </si>
   <si>
-    <t>Rush multiplier check</t>
-  </si>
-  <si>
-    <t>Flags any multiplier that is not on the list</t>
-  </si>
-  <si>
     <t>Rate used</t>
   </si>
   <si>
@@ -459,7 +480,7 @@
     <t>PRICE IMPACT (rounded up)</t>
   </si>
   <si>
-    <t>Put this on the change order as + price</t>
+    <t>Put this on the change order as "+ price"</t>
   </si>
   <si>
     <t>NEW PROJECT TOTAL</t>
@@ -468,7 +489,7 @@
     <t>current total + price impact</t>
   </si>
   <si>
-    <t>Wording for the change order: guide Chapter 3 and scripts-and-templates.txt section 4.</t>
+    <t>The change-order wording is in the guide (Chapter 3) and in scripts-and-templates.txt section 4.</t>
   </si>
   <si>
     <t>Rate Increase: what happens if some clients leave?</t>
@@ -544,9 +565,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -571,7 +591,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -581,11 +601,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2A44"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF4E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -618,19 +633,326 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF16233A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF16233A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFDE9E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF16233A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF16233A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFEFE8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E1E24"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF4C2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF16233A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3ECF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1063,110 +1385,131 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="A15" s="4"/>
       <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4"/>
+      <c r="A21" s="4">
+        <f>HYPERLINK("#'Floor Rate'!A1","Floor Rate")</f>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f>HYPERLINK("#'Floor Rate'!A1","Floor Rate")</f>
+        <f>HYPERLINK("#'Market Check'!A1","Market Check")</f>
       </c>
       <c r="B22" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <f>HYPERLINK("#'Market Check'!A1","Market Check")</f>
+        <f>HYPERLINK("#'3-Tier Quote'!A1","3-Tier Quote")</f>
       </c>
       <c r="B23" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <f>HYPERLINK("#'3-Tier Quote'!A1","3-Tier Quote")</f>
+        <f>HYPERLINK("#'Change Order'!A1","Change Order")</f>
       </c>
       <c r="B24" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <f>HYPERLINK("#'Change Order'!A1","Change Order")</f>
+        <f>HYPERLINK("#'Rate Increase'!A1","Rate Increase")</f>
       </c>
       <c r="B25" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <f>HYPERLINK("#'Rate Increase'!A1","Rate Increase")</f>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
+      <c r="A27" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="B27" s="4"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="B28" s="4"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1"/>
+  <conditionalFormatting sqref="A16:B16">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:B20">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1174,13 +1517,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1193,7 +1535,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1203,191 +1545,213 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B6" s="5">
         <v>60000</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B7" s="5">
         <v>6000</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B8" s="6">
         <v>0.25</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="6">
         <v>0.1</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B10" s="7">
         <v>44</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B11" s="7">
         <v>40</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="6">
         <v>0.6</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="7">
         <v>8</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6">
-        <f>IF(B7&gt;=1,0,(B5/(1-B7)+B6)*(1+B8))</f>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B16" s="8">
+        <f>IF(B8&gt;=1,0,(B6/(1-B8)+B7)*(1+B9))</f>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6">
-        <f>B9*B10*B11</f>
-      </c>
-      <c r="D14" s="4" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B17" s="8">
+        <f>B10*B11*B12</f>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="8">
-        <f>IF(C14&gt;0,C13/C14,0)</f>
-      </c>
-      <c r="D15" s="4" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B18" s="9">
+        <f>IF(B17&gt;0,B16/B17,0)</f>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6">
-        <f>IF(C15&gt;0,CEILING(C15,5),0)</f>
-      </c>
-      <c r="D16" s="4" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="B19" s="8">
+        <f>IF(B18&gt;0,CEILING(B18,5),0)</f>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6">
-        <f>C16*B12</f>
-      </c>
-      <c r="D17" s="4" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B20" s="8">
+        <f>B19*B13</f>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6">
-        <f>C13/12</f>
-      </c>
-      <c r="D18" s="4" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B21" s="8">
+        <f>B16/12</f>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="9">
-        <f>IF(B9&gt;0,C14/B9,0)</f>
-      </c>
-      <c r="D19" s="4" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>74</v>
       </c>
+      <c r="B22" s="10">
+        <f>IF(B10&gt;0,B17/B10,0)</f>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1"/>
+  <conditionalFormatting sqref="A5:C5">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:C15">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B13">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B22">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1395,200 +1759,196 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="56" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="4" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="4" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="B11" s="5">
         <v>90</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B14" s="8">
+        <f>'Floor Rate'!B19</f>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="6">
-        <f>'Floor Rate'!C16</f>
-      </c>
-      <c r="E12" s="4" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="B15" s="11">
+        <f>COUNT(B5:B9)</f>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11">
-        <f>COUNT(B5:B9)</f>
-      </c>
-      <c r="E13" s="4" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B16" s="8">
+        <f>IF(B15=0,"",MIN(B5:B9))</f>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="6">
-        <f>IF(D13=0,"",MIN(B5:B9))</f>
-      </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="B17" s="8">
+        <f>IF(B15=0,"",AVERAGE(B5:B9))</f>
+      </c>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="6">
-        <f>IF(D13=0,"",AVERAGE(B5:B9))</f>
-      </c>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B18" s="8">
+        <f>IF(B15=0,"",MAX(B5:B9))</f>
+      </c>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="6">
-        <f>IF(D13=0,"",MAX(B5:B9))</f>
-      </c>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="B19" s="4">
+        <f>IF(B11="","",IF(B11&lt;B14,"BELOW FLOOR","OK: at or above floor"))</f>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="6">
-        <f>IF(B11="","",IF(B11&lt;D12,"BELOW FLOOR","OK: at or above floor"))</f>
-      </c>
-      <c r="E17" s="4" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B20" s="4">
+        <f>IF(OR(B11="",B15=0),"Add market rates above",IF(B11&lt;B17,"Below market average","At or above average"))</f>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="6">
-        <f>IF(OR(B11="",D13=0),"Add market rates above",IF(B11&lt;D15,"Below market average","At or above average"))</f>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>99</v>
-      </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1"/>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="containsText" dxfId="8" priority="1">
+      <formula>NOT(ISERROR(SEARCH("BELOW FLOOR",B19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:C9">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:C13">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:B20">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1596,486 +1956,609 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="8">
+        <f>'Floor Rate'!B19</f>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="B7" s="8">
+        <f>IF(N(B6)&gt;0,B6,B5)</f>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B8" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="10">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="7">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C13" s="7">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
-        <f>IF(AND(ISNUMBER(B5),ISNUMBER(C5)),IF(C5&lt;=1,B5,0),0)</f>
-      </c>
-      <c r="E5" s="4">
-        <f>IF(AND(ISNUMBER(B5),ISNUMBER(C5)),IF(C5&lt;=2,B5,0),0)</f>
-      </c>
-      <c r="F5" s="4">
-        <f>IF(AND(ISNUMBER(B5),ISNUMBER(C5)),IF(C5&lt;=3,B5,0),0)</f>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="D13" s="10">
+        <f>IF(AND(ISNUMBER(B13),ISNUMBER(C13)),IF(C13&lt;=1,B13,0),0)</f>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(AND(ISNUMBER(B13),ISNUMBER(C13)),IF(C13&lt;=2,B13,0),0)</f>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(AND(ISNUMBER(B13),ISNUMBER(C13)),IF(C13&lt;=3,B13,0),0)</f>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="7">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="10">
+        <f>IF(AND(ISNUMBER(B14),ISNUMBER(C14)),IF(C14&lt;=1,B14,0),0)</f>
+      </c>
+      <c r="E14" s="10">
+        <f>IF(AND(ISNUMBER(B14),ISNUMBER(C14)),IF(C14&lt;=2,B14,0),0)</f>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(AND(ISNUMBER(B14),ISNUMBER(C14)),IF(C14&lt;=3,B14,0),0)</f>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="7">
+        <v>4</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10">
+        <f>IF(AND(ISNUMBER(B15),ISNUMBER(C15)),IF(C15&lt;=1,B15,0),0)</f>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(AND(ISNUMBER(B15),ISNUMBER(C15)),IF(C15&lt;=2,B15,0),0)</f>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(AND(ISNUMBER(B15),ISNUMBER(C15)),IF(C15&lt;=3,B15,0),0)</f>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="7">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7">
+        <v>2</v>
+      </c>
+      <c r="D16" s="10">
+        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C16)),IF(C16&lt;=1,B16,0),0)</f>
+      </c>
+      <c r="E16" s="10">
+        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C16)),IF(C16&lt;=2,B16,0),0)</f>
+      </c>
+      <c r="F16" s="10">
+        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C16)),IF(C16&lt;=3,B16,0),0)</f>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7">
+        <v>2</v>
+      </c>
+      <c r="D17" s="10">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),IF(C17&lt;=1,B17,0),0)</f>
+      </c>
+      <c r="E17" s="10">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),IF(C17&lt;=2,B17,0),0)</f>
+      </c>
+      <c r="F17" s="10">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),IF(C17&lt;=3,B17,0),0)</f>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="7">
+        <v>5</v>
+      </c>
+      <c r="C18" s="7">
+        <v>3</v>
+      </c>
+      <c r="D18" s="10">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),IF(C18&lt;=1,B18,0),0)</f>
+      </c>
+      <c r="E18" s="10">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),IF(C18&lt;=2,B18,0),0)</f>
+      </c>
+      <c r="F18" s="10">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),IF(C18&lt;=3,B18,0),0)</f>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="10">
+        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),IF(C19&lt;=1,B19,0),0)</f>
+      </c>
+      <c r="E19" s="10">
+        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),IF(C19&lt;=2,B19,0),0)</f>
+      </c>
+      <c r="F19" s="10">
+        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),IF(C19&lt;=3,B19,0),0)</f>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="10">
+        <f>IF(AND(ISNUMBER(B20),ISNUMBER(C20)),IF(C20&lt;=1,B20,0),0)</f>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(AND(ISNUMBER(B20),ISNUMBER(C20)),IF(C20&lt;=2,B20,0),0)</f>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(AND(ISNUMBER(B20),ISNUMBER(C20)),IF(C20&lt;=3,B20,0),0)</f>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="10">
+        <f>IF(AND(ISNUMBER(B21),ISNUMBER(C21)),IF(C21&lt;=1,B21,0),0)</f>
+      </c>
+      <c r="E21" s="10">
+        <f>IF(AND(ISNUMBER(B21),ISNUMBER(C21)),IF(C21&lt;=2,B21,0),0)</f>
+      </c>
+      <c r="F21" s="10">
+        <f>IF(AND(ISNUMBER(B21),ISNUMBER(C21)),IF(C21&lt;=3,B21,0),0)</f>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="10">
+        <f>IF(AND(ISNUMBER(B22),ISNUMBER(C22)),IF(C22&lt;=1,B22,0),0)</f>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(AND(ISNUMBER(B22),ISNUMBER(C22)),IF(C22&lt;=2,B22,0),0)</f>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(AND(ISNUMBER(B22),ISNUMBER(C22)),IF(C22&lt;=3,B22,0),0)</f>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="10">
+        <f>IF(AND(ISNUMBER(B23),ISNUMBER(C23)),IF(C23&lt;=1,B23,0),0)</f>
+      </c>
+      <c r="E23" s="10">
+        <f>IF(AND(ISNUMBER(B23),ISNUMBER(C23)),IF(C23&lt;=2,B23,0),0)</f>
+      </c>
+      <c r="F23" s="10">
+        <f>IF(AND(ISNUMBER(B23),ISNUMBER(C23)),IF(C23&lt;=3,B23,0),0)</f>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="10">
+        <f>IF(AND(ISNUMBER(B24),ISNUMBER(C24)),IF(C24&lt;=1,B24,0),0)</f>
+      </c>
+      <c r="E24" s="10">
+        <f>IF(AND(ISNUMBER(B24),ISNUMBER(C24)),IF(C24&lt;=2,B24,0),0)</f>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(AND(ISNUMBER(B24),ISNUMBER(C24)),IF(C24&lt;=3,B24,0),0)</f>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="10">
+        <f>IF(AND(ISNUMBER(B25),ISNUMBER(C25)),IF(C25&lt;=1,B25,0),0)</f>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(AND(ISNUMBER(B25),ISNUMBER(C25)),IF(C25&lt;=2,B25,0),0)</f>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(AND(ISNUMBER(B25),ISNUMBER(C25)),IF(C25&lt;=3,B25,0),0)</f>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="10">
+        <f>IF(AND(ISNUMBER(B26),ISNUMBER(C26)),IF(C26&lt;=1,B26,0),0)</f>
+      </c>
+      <c r="E26" s="10">
+        <f>IF(AND(ISNUMBER(B26),ISNUMBER(C26)),IF(C26&lt;=2,B26,0),0)</f>
+      </c>
+      <c r="F26" s="10">
+        <f>IF(AND(ISNUMBER(B26),ISNUMBER(C26)),IF(C26&lt;=3,B26,0),0)</f>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="10">
+        <f>IF(AND(ISNUMBER(B27),ISNUMBER(C27)),IF(C27&lt;=1,B27,0),0)</f>
+      </c>
+      <c r="E27" s="10">
+        <f>IF(AND(ISNUMBER(B27),ISNUMBER(C27)),IF(C27&lt;=2,B27,0),0)</f>
+      </c>
+      <c r="F27" s="10">
+        <f>IF(AND(ISNUMBER(B27),ISNUMBER(C27)),IF(C27&lt;=3,B27,0),0)</f>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="10">
+        <f>SUM(D13:D27)</f>
+      </c>
+      <c r="E28" s="10">
+        <f>SUM(E13:E27)</f>
+      </c>
+      <c r="F28" s="10">
+        <f>SUM(F13:F27)</f>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="10">
-        <v>12</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <f>IF(AND(ISNUMBER(B6),ISNUMBER(C6)),IF(C6&lt;=1,B6,0),0)</f>
-      </c>
-      <c r="E6" s="4">
-        <f>IF(AND(ISNUMBER(B6),ISNUMBER(C6)),IF(C6&lt;=2,B6,0),0)</f>
-      </c>
-      <c r="F6" s="4">
-        <f>IF(AND(ISNUMBER(B6),ISNUMBER(C6)),IF(C6&lt;=3,B6,0),0)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="10">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <f>IF(AND(ISNUMBER(B7),ISNUMBER(C7)),IF(C7&lt;=1,B7,0),0)</f>
-      </c>
-      <c r="E7" s="4">
-        <f>IF(AND(ISNUMBER(B7),ISNUMBER(C7)),IF(C7&lt;=2,B7,0),0)</f>
-      </c>
-      <c r="F7" s="4">
-        <f>IF(AND(ISNUMBER(B7),ISNUMBER(C7)),IF(C7&lt;=3,B7,0),0)</f>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="10">
-        <v>6</v>
-      </c>
-      <c r="C8" s="10">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4">
-        <f>IF(AND(ISNUMBER(B8),ISNUMBER(C8)),IF(C8&lt;=1,B8,0),0)</f>
-      </c>
-      <c r="E8" s="4">
-        <f>IF(AND(ISNUMBER(B8),ISNUMBER(C8)),IF(C8&lt;=2,B8,0),0)</f>
-      </c>
-      <c r="F8" s="4">
-        <f>IF(AND(ISNUMBER(B8),ISNUMBER(C8)),IF(C8&lt;=3,B8,0),0)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="10">
-        <v>2</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="4">
-        <f>IF(AND(ISNUMBER(B9),ISNUMBER(C9)),IF(C9&lt;=1,B9,0),0)</f>
-      </c>
-      <c r="E9" s="4">
-        <f>IF(AND(ISNUMBER(B9),ISNUMBER(C9)),IF(C9&lt;=2,B9,0),0)</f>
-      </c>
-      <c r="F9" s="4">
-        <f>IF(AND(ISNUMBER(B9),ISNUMBER(C9)),IF(C9&lt;=3,B9,0),0)</f>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="10">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4">
-        <f>IF(AND(ISNUMBER(B10),ISNUMBER(C10)),IF(C10&lt;=1,B10,0),0)</f>
-      </c>
-      <c r="E10" s="4">
-        <f>IF(AND(ISNUMBER(B10),ISNUMBER(C10)),IF(C10&lt;=2,B10,0),0)</f>
-      </c>
-      <c r="F10" s="4">
-        <f>IF(AND(ISNUMBER(B10),ISNUMBER(C10)),IF(C10&lt;=3,B10,0),0)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="4">
-        <f>IF(AND(ISNUMBER(B11),ISNUMBER(C11)),IF(C11&lt;=1,B11,0),0)</f>
-      </c>
-      <c r="E11" s="4">
-        <f>IF(AND(ISNUMBER(B11),ISNUMBER(C11)),IF(C11&lt;=2,B11,0),0)</f>
-      </c>
-      <c r="F11" s="4">
-        <f>IF(AND(ISNUMBER(B11),ISNUMBER(C11)),IF(C11&lt;=3,B11,0),0)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="4">
-        <f>IF(AND(ISNUMBER(B12),ISNUMBER(C12)),IF(C12&lt;=1,B12,0),0)</f>
-      </c>
-      <c r="E12" s="4">
-        <f>IF(AND(ISNUMBER(B12),ISNUMBER(C12)),IF(C12&lt;=2,B12,0),0)</f>
-      </c>
-      <c r="F12" s="4">
-        <f>IF(AND(ISNUMBER(B12),ISNUMBER(C12)),IF(C12&lt;=3,B12,0),0)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="4">
-        <f>IF(AND(ISNUMBER(B13),ISNUMBER(C13)),IF(C13&lt;=1,B13,0),0)</f>
-      </c>
-      <c r="E13" s="4">
-        <f>IF(AND(ISNUMBER(B13),ISNUMBER(C13)),IF(C13&lt;=2,B13,0),0)</f>
-      </c>
-      <c r="F13" s="4">
-        <f>IF(AND(ISNUMBER(B13),ISNUMBER(C13)),IF(C13&lt;=3,B13,0),0)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="4">
-        <f>IF(AND(ISNUMBER(B14),ISNUMBER(C14)),IF(C14&lt;=1,B14,0),0)</f>
-      </c>
-      <c r="E14" s="4">
-        <f>IF(AND(ISNUMBER(B14),ISNUMBER(C14)),IF(C14&lt;=2,B14,0),0)</f>
-      </c>
-      <c r="F14" s="4">
-        <f>IF(AND(ISNUMBER(B14),ISNUMBER(C14)),IF(C14&lt;=3,B14,0),0)</f>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="4">
-        <f>IF(AND(ISNUMBER(B15),ISNUMBER(C15)),IF(C15&lt;=1,B15,0),0)</f>
-      </c>
-      <c r="E15" s="4">
-        <f>IF(AND(ISNUMBER(B15),ISNUMBER(C15)),IF(C15&lt;=2,B15,0),0)</f>
-      </c>
-      <c r="F15" s="4">
-        <f>IF(AND(ISNUMBER(B15),ISNUMBER(C15)),IF(C15&lt;=3,B15,0),0)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="4">
-        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C16)),IF(C16&lt;=1,B16,0),0)</f>
-      </c>
-      <c r="E16" s="4">
-        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C16)),IF(C16&lt;=2,B16,0),0)</f>
-      </c>
-      <c r="F16" s="4">
-        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C16)),IF(C16&lt;=3,B16,0),0)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="4">
-        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),IF(C17&lt;=1,B17,0),0)</f>
-      </c>
-      <c r="E17" s="4">
-        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),IF(C17&lt;=2,B17,0),0)</f>
-      </c>
-      <c r="F17" s="4">
-        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),IF(C17&lt;=3,B17,0),0)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="4">
-        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),IF(C18&lt;=1,B18,0),0)</f>
-      </c>
-      <c r="E18" s="4">
-        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),IF(C18&lt;=2,B18,0),0)</f>
-      </c>
-      <c r="F18" s="4">
-        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),IF(C18&lt;=3,B18,0),0)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="4">
-        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),IF(C19&lt;=1,B19,0),0)</f>
-      </c>
-      <c r="E19" s="4">
-        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),IF(C19&lt;=2,B19,0),0)</f>
-      </c>
-      <c r="F19" s="4">
-        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),IF(C19&lt;=3,B19,0),0)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="4">
-        <f>SUM(D5:D19)</f>
-      </c>
-      <c r="E20" s="4">
-        <f>SUM(E5:E19)</f>
-      </c>
-      <c r="F20" s="4">
-        <f>SUM(F5:F19)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B25" s="10">
-        <v>50</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="6">
-        <f>'Floor Rate'!C16</f>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="6">
-        <f>IF(N(B22)&gt;0,B22,D26)</f>
-      </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="8">
-        <f>D20*$D$27*(1+$B$23)</f>
-      </c>
-      <c r="E29" s="8">
-        <f>E20*$D$27*(1+$B$23)</f>
-      </c>
-      <c r="F29" s="8">
-        <f>F20*$D$27*(1+$B$23)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="6">
-        <f>IF(D29&lt;=0,0,IF(N($B$25)&gt;0,CEILING(D29,$B$25),D29))</f>
-      </c>
-      <c r="E30" s="6">
-        <f>IF(E29&lt;=0,0,IF(N($B$25)&gt;0,CEILING(E29,$B$25),E29))</f>
-      </c>
-      <c r="F30" s="6">
-        <f>IF(F29&lt;=0,0,IF(N($B$25)&gt;0,CEILING(F29,$B$25),F29))</f>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F30" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="6">
-        <f>D30*$B$24</f>
-      </c>
-      <c r="E31" s="6">
-        <f>E30*$B$24</f>
-      </c>
-      <c r="F31" s="6">
-        <f>F30*$B$24</f>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="B31" s="10">
+        <f>D28</f>
+      </c>
+      <c r="C31" s="9">
+        <f>B31*$B$7*(1+$B$8)</f>
+      </c>
+      <c r="D31" s="8">
+        <f>IF(C31&lt;=0,0,IF(N($B$10)&gt;0,CEILING(C31,$B$10),C31))</f>
+      </c>
+      <c r="E31" s="8">
+        <f>D31*$B$9</f>
+      </c>
+      <c r="F31" s="8">
+        <f>D31-E31</f>
+      </c>
+      <c r="G31" s="9">
+        <f>IF(B31&gt;0,D31/B31,0)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="6">
-        <f>D30-D31</f>
-      </c>
-      <c r="E32" s="6">
-        <f>E30-E31</f>
-      </c>
-      <c r="F32" s="6">
-        <f>F30-F31</f>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="B32" s="10">
+        <f>E28</f>
+      </c>
+      <c r="C32" s="9">
+        <f>B32*$B$7*(1+$B$8)</f>
+      </c>
+      <c r="D32" s="8">
+        <f>IF(C32&lt;=0,0,IF(N($B$10)&gt;0,CEILING(C32,$B$10),C32))</f>
+      </c>
+      <c r="E32" s="8">
+        <f>D32*$B$9</f>
+      </c>
+      <c r="F32" s="8">
+        <f>D32-E32</f>
+      </c>
+      <c r="G32" s="9">
+        <f>IF(B32&gt;0,D32/B32,0)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+        <v>134</v>
+      </c>
+      <c r="B33" s="10">
+        <f>F28</f>
+      </c>
+      <c r="C33" s="9">
+        <f>B33*$B$7*(1+$B$8)</f>
+      </c>
       <c r="D33" s="8">
-        <f>IF(D20&gt;0,D30/D20,0)</f>
+        <f>IF(C33&lt;=0,0,IF(N($B$10)&gt;0,CEILING(C33,$B$10),C33))</f>
       </c>
       <c r="E33" s="8">
-        <f>IF(E20&gt;0,E30/E20,0)</f>
+        <f>D33*$B$9</f>
       </c>
       <c r="F33" s="8">
-        <f>IF(F20&gt;0,F30/F20,0)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <f>D33-E33</f>
+      </c>
+      <c r="G33" s="9">
+        <f>IF(B33&gt;0,D33/B33,0)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+        <v>135</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1"/>
+  <conditionalFormatting sqref="A12:F12">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:G30">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:B10">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:C27">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:F28">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:G33">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="1 = all packages, 2 = Standard + Premium, 3 = Premium only" showErrorMessage="1" sqref="C13:C27">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2083,26 +2566,25 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -2112,159 +2594,166 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="7">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="C6" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="6">
         <v>0.15</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="C7" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="10">
+        <v>144</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="7">
         <v>25</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" s="10">
+      <c r="C10" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="5">
         <v>2700</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="6">
-        <f>IF(OR(B7=1,B7=1.25,B7=1.5),"OK","Use 1, 1.25 or 1.5")</f>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="6">
-        <f>IF(N(B8)&gt;0,B8,'3-Tier Quote'!D27)</f>
-      </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="8">
-        <f>B5*(1+B6)*C13*B7</f>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="B14" s="8">
+        <f>IF(N(B9)&gt;0,B9,'3-Tier Quote'!B7)</f>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="6">
-        <f>IF(B5*(1+B6)*C13*B7&lt;=0,0,CEILING(B5*(1+B6)*C13*B7,IF(N(B9)&gt;0,B9,1)))</f>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="B15" s="9">
+        <f>B6*(1+B7)*B14*B8</f>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="6">
-        <f>B10+C15</f>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="B16" s="8">
+        <f>IF(B6*(1+B7)*B14*B8&lt;=0,0,CEILING(B6*(1+B7)*B14*B8,IF(N(B10)&gt;0,B10,1)))</f>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="8">
+        <f>B11+B16</f>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1"/>
+  <conditionalFormatting sqref="A5:C5">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:C13">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B11">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:B17">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" showInputMessage="1" prompt="1 = normal, 1.25 = rush, 1.5 = urgent" showErrorMessage="1" sqref="B8">
+      <formula1>"1,1.25,1.5"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2272,26 +2761,25 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -2301,147 +2789,167 @@
       <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="5">
         <v>90</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="C6" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="5">
         <v>100</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="C7" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="7">
         <v>88</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="C8" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="6">
         <v>0.05</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6">
-        <f>B5*B7</f>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="9">
-        <f>B7*(1-B8)</f>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6">
-        <f>B6*C11</f>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="B12" s="8">
+        <f>B6*B8</f>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6">
-        <f>C12-C10</f>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="B13" s="10">
+        <f>B8*(1-B9)</f>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="12">
-        <f>IF(N(B6)&gt;0,1-B5/B6,0)</f>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="B14" s="8">
+        <f>B7*B13</f>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6">
-        <f>IF(N(B6)&lt;=0,"",IF(ROUND(B8-C14,6)&lt;0,"You earn more, even with the loss",IF(ROUND(B8-C14,6)=0,"Break-even","You earn less: raise less or keep more clients")))</f>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="B15" s="8">
+        <f>B14-B12</f>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="9">
-        <f>B7-C11</f>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
+      </c>
+      <c r="B16" s="12">
+        <f>IF(N(B7)&gt;0,1-B6/B7,0)</f>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="4">
+        <f>IF(N(B7)&lt;=0,"",IF(ROUND(B9-B16,6)&lt;0,"You earn more, even with the loss",IF(ROUND(B9-B16,6)=0,"Break-even","You earn less: raise less or keep more clients")))</f>
+      </c>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" s="10">
+        <f>B8-B13</f>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1"/>
+  <conditionalFormatting sqref="A5:C5">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11:C11">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:B9">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B18">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="greaterThan">
+      <formula>-999999999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
